--- a/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v16.xlsx
+++ b/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v16.xlsx
@@ -20,10 +20,10 @@
     <sheet name="Resumen de observaciones" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historia de usuario'!$A$5:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Historia de usuario'!$A$5:$F$61</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Historia de usuario'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Flujo del app'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CEO'!$A$9:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CEO'!$A$9:$I$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'CEO'!$9:$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gerente'!$A$9:$I$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Gerente'!$9:$9</definedName>
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -739,14 +739,14 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Ser administrador (CEO, Gerente, Director, Jefe)</t>
+          <t>Perfil Administrador (asignable)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Director de Proyectos</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
+          <t>Asigna el perfil de cada cargo (Administrador u Operativo) para controlar los accesos a la información.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Crear · Configuración (barra lateral)</t>
+          <t>Parametrización · Perfiles y accesos</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Catálogos, bases y ventas administrados</t>
+          <t>Accesos controlados, con mínimo un administrador</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Ser administrador (CEO, Gerente, Director, Jefe)</t>
+          <t>Perfil Administrador</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Diseñador</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -788,29 +788,29 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Gestiona todo lo operativo sin ver costos ni configuración: su bandeja, sus actividades, el calendario y las fichas.</t>
+          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Resumen · Actividades · Mi trabajo · Calendario</t>
+          <t>Crear · Configuración (barra lateral)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Gestión operativa completa de su frente</t>
+          <t>Catálogos, bases y ventas administrados</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Cualquier cargo</t>
+          <t>Perfil Administrador (asignable)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -820,29 +820,29 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
+          <t>Asigna el perfil de cada cargo (Administrador u Operativo) para controlar los accesos a la información.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Crear · Configuración (barra lateral)</t>
+          <t>Parametrización · Perfiles y accesos</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Catálogos, bases y ventas administrados</t>
+          <t>Accesos controlados, con mínimo un administrador</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Ser administrador (CEO, Gerente, Director, Jefe)</t>
+          <t>Perfil Administrador</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 1</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 2</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -884,29 +884,29 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Gestiona todo lo operativo sin ver costos ni configuración: su bandeja, sus actividades, el calendario y las fichas.</t>
+          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Resumen · Actividades · Mi trabajo · Calendario</t>
+          <t>Crear · Configuración (barra lateral)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Gestión operativa completa de su frente</t>
+          <t>Catálogos, bases y ventas administrados</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Cualquier cargo</t>
+          <t>Perfil Administrador (asignable)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -916,317 +916,317 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
+          <t>Asigna el perfil de cada cargo (Administrador u Operativo) para controlar los accesos a la información.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Crear · Configuración (barra lateral)</t>
+          <t>Parametrización · Perfiles y accesos</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Catálogos, bases y ventas administrados</t>
+          <t>Accesos controlados, con mínimo un administrador</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Ser administrador (CEO, Gerente, Director, Jefe)</t>
+          <t>Perfil Administrador</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Épica 0 · Modelo de administradores y accesos</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Gestiona todo lo operativo sin ver costos ni configuración: su bandeja, sus actividades, el calendario y las fichas.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Mi trabajo · Calendario</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Gestión operativa completa de su frente</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Cualquier cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 2</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Épica 0 · Modelo de administradores y accesos</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Gestiona todo lo operativo sin ver costos ni configuración: su bandeja, sus actividades, el calendario y las fichas.</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Mi trabajo · Calendario</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Gestión operativa completa de su frente</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Cualquier cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Épica 0 · Modelo de administradores y accesos</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Administra: crea proyectos, ve los costos, carga las bases de Excel y gestiona Parametrización y Bases y auditoría.</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Crear · Configuración (barra lateral)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Catálogos, bases y ventas administrados</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Perfil Administrador (asignable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Épica 0 · Modelo de administradores y accesos</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Asigna el perfil de cada cargo (Administrador u Operativo) para controlar los accesos a la información.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Parametrización · Perfiles y accesos</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Accesos controlados, con mínimo un administrador</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Perfil Administrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
           <t>Supervisor Contactabilidad</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Épica 0 · Modelo de administradores y accesos</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Gestiona todo lo operativo sin ver costos ni configuración: su bandeja, sus actividades, el calendario y las fichas.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Resumen · Actividades · Mi trabajo · Calendario</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Gestión operativa completa de su frente</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Cualquier cargo</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Épica 1 · Venta y registro (botón «Crear»)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Registra la venta con «Crear»: catálogos, productos con horas y fecha solicitada, contactos; activación automática con 14 validaciones.</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Crear (barra superior)</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Proyecto Activo con asignaciones por cargo</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Ser administrador (RN-01)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Director de Proyectos</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Épica 1 · Venta y registro (botón «Crear»)</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Registra la venta con «Crear»: catálogos, productos con horas y fecha solicitada, contactos; activación automática con 14 validaciones.</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Crear (barra superior)</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>Proyecto Activo con asignaciones por cargo</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Ser administrador (RN-01)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Épica 1 · Venta y registro (botón «Crear»)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Registra la venta con «Crear»: catálogos, productos con horas y fecha solicitada, contactos; activación automática con 14 validaciones.</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Crear (barra superior)</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Proyecto Activo con asignaciones por cargo</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Ser administrador (RN-01)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Jefe de Operaciones</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Épica 1 · Venta y registro (botón «Crear»)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Registra la venta con «Crear»: catálogos, productos con horas y fecha solicitada, contactos; activación automática con 14 validaciones.</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Crear (barra superior)</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Proyecto Activo con asignaciones por cargo</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Ser administrador (RN-01)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Épica 2 · Aceptación y negociación</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Resuelve los ajustes de todos los cargos desde «Para resolver como dirección» (cuatro decisiones).</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Negociaciones resueltas con historial</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>Ajuste propuesto por un líder o coordinador</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Épica 2 · Aceptación y negociación</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Acepta o negocia la asignación de mediciones objetivas; las tarjetas en ajuste dicen «decide la administración».</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Asignación aceptada o en negociación con historial</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Tarea generada por el motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Épica 2 · Aceptación y negociación</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Resuelve los ajustes de todos los cargos desde «Para resolver como dirección» (cuatro decisiones).</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Negociaciones resueltas con historial</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Ajuste propuesto por un líder o coordinador</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Diseñador</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Épica 2 · Aceptación y negociación</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Acepta o negocia la asignación de diseño; las tarjetas en ajuste dicen «decide la administración».</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Asignación aceptada o en negociación con historial</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Tarea generada por el motor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1258,7 +1258,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 1</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Acepta o negocia la asignación de Tablero BI; las tarjetas en ajuste dicen «decide la administración».</t>
+          <t>Acepta o negocia la asignación de mediciones objetivas; las tarjetas en ajuste dicen «decide la administración».</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 1</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1300,29 +1300,29 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Se reparte el trabajo con su gestor gemelo mediante «Reasignar cargo» (directo entre gestores).</t>
+          <t>Resuelve los ajustes de todos los cargos desde «Para resolver como dirección» (cuatro decisiones).</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Mi trabajo · Reasignar cargo</t>
+          <t>Mi trabajo</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Producto reasignado con bitácora</t>
+          <t>Negociaciones resueltas con historial</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Producto del frente de datos</t>
+          <t>Ajuste propuesto por un líder o coordinador</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 2</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -1332,29 +1332,29 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Se reparte el trabajo con su gestor gemelo mediante «Reasignar cargo» (directo entre gestores).</t>
+          <t>Acepta o negocia la asignación de diseño; las tarjetas en ajuste dicen «decide la administración».</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Mi trabajo · Reasignar cargo</t>
+          <t>Mi trabajo</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Producto reasignado con bitácora</t>
+          <t>Asignación aceptada o en negociación con historial</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Producto del frente de datos</t>
+          <t>Tarea generada por el motor</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Gerente</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1386,167 +1386,167 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Épica 2 · Aceptación y negociación</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Acepta o negocia la asignación de Tablero BI; las tarjetas en ajuste dicen «decide la administración».</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Asignación aceptada o en negociación con historial</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Tarea generada por el motor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Épica 2 · Aceptación y negociación</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Se reparte el trabajo con su gestor gemelo mediante «Reasignar cargo» (directo entre gestores).</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Mi trabajo · Reasignar cargo</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Producto reasignado con bitácora</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Producto del frente de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 2</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Épica 2 · Aceptación y negociación</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Se reparte el trabajo con su gestor gemelo mediante «Reasignar cargo» (directo entre gestores).</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Mi trabajo · Reasignar cargo</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Producto reasignado con bitácora</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Producto del frente de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Épica 2 · Aceptación y negociación</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Resuelve los ajustes de todos los cargos desde «Para resolver como dirección» (cuatro decisiones).</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Negociaciones resueltas con historial</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Ajuste propuesto por un líder o coordinador</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>Supervisor Contactabilidad</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Épica 2 · Aceptación y negociación</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Acepta o negocia la asignación de cápsulas; las tarjetas en ajuste dicen «decide la administración».</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Mi trabajo</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Asignación aceptada o en negociación con historial</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Tarea generada por el motor</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Épica 3 · Requisitos de información</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Define los requisitos de mediciones objetivas; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Tarjeta del producto · Requisitos</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos trazables con ubicación</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Asignación aceptada</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>Épica 3 · Requisitos de información</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Consolida los requisitos en UNA solicitud con contacto y evidencia obligatorios.</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Ficha · Solicitud consolidada</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Solicitud trazable al cliente</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos definidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Diseñador</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Épica 3 · Requisitos de información</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Define los requisitos de diseño; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Tarjeta del producto · Requisitos</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos trazables con ubicación</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Asignación aceptada</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Gestor de Datos 1</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Épica 3 · Requisitos de información</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Define los requisitos de Tablero BI; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Tarjeta del producto · Requisitos</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos trazables con ubicación</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Asignación aceptada</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -1556,29 +1556,29 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Consolida los requisitos en UNA solicitud con contacto y evidencia obligatorios.</t>
+          <t>Define los requisitos de mediciones objetivas; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Ficha · Solicitud consolidada</t>
+          <t>Tarjeta del producto · Requisitos</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Solicitud trazable al cliente</t>
+          <t>Requisitos trazables con ubicación</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Requisitos definidos</t>
+          <t>Asignación aceptada</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Supervisor Contactabilidad</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -1588,221 +1588,221 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Define los requisitos de cápsulas; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
+          <t>Consolida los requisitos en UNA solicitud con contacto y evidencia obligatorios.</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
+          <t>Ficha · Solicitud consolidada</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Solicitud trazable al cliente</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Requisitos definidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Diseñador</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Épica 3 · Requisitos de información</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Define los requisitos de diseño; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
           <t>Tarjeta del producto · Requisitos</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Requisitos trazables con ubicación</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Asignación aceptada</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Épica 4 · Plan de trabajo final</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Construye y versiona el plan final con horas PLANIFICADAS (las vendidas no cambian); bloqueado si hay asignaciones o coordinación sin resolver.</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Ficha · sección 4</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>Plan final íntegro (RN-13, RN-14)</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Asignaciones y coordinación aceptadas</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Jefe de Operaciones</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Épica 4 · Plan de trabajo final</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Construye y versiona el plan final con horas PLANIFICADAS (las vendidas no cambian); bloqueado si hay asignaciones o coordinación sin resolver.</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Ficha · sección 4</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Plan final íntegro (RN-13, RN-14)</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Asignaciones y coordinación aceptadas</t>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Épica 3 · Requisitos de información</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Define los requisitos de Tablero BI; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Tarjeta del producto · Requisitos</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Requisitos trazables con ubicación</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Asignación aceptada</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Director de Proyectos</t>
+          <t>Jefe de Operaciones</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+          <t>Épica 3 · Requisitos de información</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+          <t>Consolida los requisitos en UNA solicitud con contacto y evidencia obligatorios.</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Mi trabajo</t>
+          <t>Ficha · Solicitud consolidada</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Panel al día y cierres automáticos con sello</t>
+          <t>Solicitud trazable al cliente</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>Ser el cargo responsable (RN-12)</t>
+          <t>Requisitos definidos</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Diseñador</t>
+          <t>Supervisor Contactabilidad</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+          <t>Épica 3 · Requisitos de información</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+          <t>Define los requisitos de cápsulas; al marcar Recibido registra la ubicación de la información (obligatoria).</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Mi trabajo</t>
+          <t>Tarjeta del producto · Requisitos</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>Panel al día y cierres automáticos con sello</t>
+          <t>Requisitos trazables con ubicación</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>Ser el cargo responsable (RN-12)</t>
+          <t>Asignación aceptada</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Gestor de Datos 1</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Panel al día y cierres automáticos con sello</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Ser el cargo responsable (RN-12)</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Director de Proyectos</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Épica 4 · Plan de trabajo final</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Construye y versiona el plan final con horas PLANIFICADAS (las vendidas no cambian); bloqueado si hay asignaciones o coordinación sin resolver.</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Ficha · sección 4</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Plan final íntegro (RN-13, RN-14)</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Asignaciones y coordinación aceptadas</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Gestor de Datos 2</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Mi trabajo</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Panel al día y cierres automáticos con sello</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>Ser el cargo responsable (RN-12)</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Épica 4 · Plan de trabajo final</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Construye y versiona el plan final con horas PLANIFICADAS (las vendidas no cambian); bloqueado si hay asignaciones o coordinación sin resolver.</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Ficha · sección 4</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Plan final íntegro (RN-13, RN-14)</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Asignaciones y coordinación aceptadas</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -1834,167 +1834,167 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
+          <t>Diseñador</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Panel al día y cierres automáticos con sello</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Ser el cargo responsable (RN-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Panel al día y cierres automáticos con sello</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Ser el cargo responsable (RN-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 2</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Panel al día y cierres automáticos con sello</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Ser el cargo responsable (RN-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Mi trabajo</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Panel al día y cierres automáticos con sello</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Ser el cargo responsable (RN-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
           <t>Supervisor Contactabilidad</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Épica 5 · Ejecución («Actualizar» e «Hitos»)</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Registra avances y retrasos con «Actualizar» y gestiona hitos (ponderados por horas) con «Hitos»; declara completado y el cierre es automático.</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Mi trabajo</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Panel al día y cierres automáticos con sello</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>Ser el cargo responsable (RN-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Resumen · Actividades · Calendario</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>Lectura del portafolio</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Resumen · Actividades · Calendario</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>Lectura del portafolio</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Diseñador</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Resumen · Actividades · Calendario</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>Lectura del portafolio</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Resumen · Actividades · Calendario</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>Lectura del portafolio</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 1</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Gestor de Datos 2</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -2058,7 +2058,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2090,167 +2090,167 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Calendario</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Lectura del portafolio</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Calendario</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Lectura del portafolio</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 2</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Calendario</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Lectura del portafolio</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>Resumen · Actividades · Calendario</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Lectura del portafolio</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
           <t>Supervisor Contactabilidad</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Transversal · Resumen, Actividades y Calendario</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Consulta Resumen, Actividades (con «Mi cargo»), Calendario (día completo clicable) y la ficha; los administradores además descargan y auditan.</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Resumen · Actividades · Calendario</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Lectura del portafolio</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>Ninguno</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>Aceptación de la versión final</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>Este archivo · Resumen de observaciones</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Sí · Con ajustes menores · No</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>Verificaciones de su pestaña terminadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Director de Proyectos</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>Aceptación de la versión final</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>Este archivo · Resumen de observaciones</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>Sí · Con ajustes menores · No</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Verificaciones de su pestaña terminadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>Diseñador</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>Aceptación de la versión final</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>Este archivo · Resumen de observaciones</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Sí · Con ajustes menores · No</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>Verificaciones de su pestaña terminadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Aceptación de la versión final</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>Este archivo · Resumen de observaciones</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>Sí · Con ajustes menores · No</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr">
-        <is>
-          <t>Verificaciones de su pestaña terminadas</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>Gestor de Datos 1</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>Gestor de Datos 2</t>
+          <t>Director de Proyectos</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -2314,7 +2314,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>Jefe de Operaciones</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -2346,49 +2346,177 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Este archivo · Resumen de observaciones</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Sí · Con ajustes menores · No</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Verificaciones de su pestaña terminadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 1</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Este archivo · Resumen de observaciones</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Sí · Con ajustes menores · No</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Verificaciones de su pestaña terminadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Gestor de Datos 2</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Este archivo · Resumen de observaciones</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Sí · Con ajustes menores · No</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Verificaciones de su pestaña terminadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Jefe de Operaciones</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Este archivo · Resumen de observaciones</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Sí · Con ajustes menores · No</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Verificaciones de su pestaña terminadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
           <t>Supervisor Contactabilidad</t>
         </is>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>Aceptación de la versión final</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>Firma la aceptación de la versión final en la tabla de decisión.</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D61" s="10" t="inlineStr">
         <is>
           <t>Este archivo · Resumen de observaciones</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>Sí · Con ajustes menores · No</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>Verificaciones de su pestaña terminadas</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Fuente: Especificación funcional y flujograma del proceso de gestión de proyectos, versión 1.1, Rehavid S.A.S. Ronda de aceptación sobre la versión 16 (final): modelo de administradores (CEO, Gerente, Director, Jefe), costos restringidos, y los hallazgos de la tercera ronda aplicados (plan con horas planificadas, coordinación bloqueante, ubicación obligatoria, reasignación entre gestores, calendario uniforme). Los pasos 1 a 11 corresponden al numeral 7 de la especificación.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F57"/>
+  <autoFilter ref="A5:F61"/>
   <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A63:F63"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3742,7 +3870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3915,17 +4043,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Cargar una base como administrador</t>
+          <t>Asignar perfiles de acceso</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Cargue Base_BI.xlsx desde Bases y auditoría; observe el resumen y el aviso «Base cargada con éxito». Revise en la hoja Productos del Excel la columna nueva «responsable» (la fase 2 trae «Gestor de Datos 2» de ejemplo).</t>
+          <t>En Parametrización → «Perfiles y accesos» cambie el Supervisor Contactabilidad a Administrador; verifique con su sesión que gana Configuración, costos y el botón «Crear», y devuélvalo a Operativo. Intente dejar cero administradores.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>La carga es tarea de administradores; la columna responsable permite dirigir un producto a un cargo puntual desde el Excel (p. ej. repartir entre los Gestores de Datos).</t>
+          <t>El perfil de cada cargo se asigna aquí y rige de inmediato; la aplicación impide quedarse sin administradores y el cambio queda guardado con el respaldo.</t>
         </is>
       </c>
       <c r="F11" s="19" t="n"/>
@@ -3939,22 +4067,22 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Épica 2 · Aceptación y negociación</t>
+          <t>Épica 0 · Modelo de administradores y accesos</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Resolver desde «Para resolver como dirección»</t>
+          <t>Cargar una base como administrador</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>En Mi trabajo resuelva uno de los casos demo con las cuatro decisiones.</t>
+          <t>Cargue Base_BI.xlsx desde Bases y auditoría; observe el resumen y el aviso «Base cargada con éxito». Revise en la hoja Productos del Excel la columna nueva «responsable» (la fase 2 trae «Gestor de Datos 2» de ejemplo).</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>La sección concentra los ajustes de todos los cargos; cada decisión queda en el historial.</t>
+          <t>La carga es tarea de administradores; la columna responsable permite dirigir un producto a un cargo puntual desde el Excel (p. ej. repartir entre los Gestores de Datos).</t>
         </is>
       </c>
       <c r="F12" s="19" t="n"/>
@@ -3968,22 +4096,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Épica 4 · Plan de trabajo final</t>
+          <t>Épica 2 · Aceptación y negociación</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Verificar la integridad comercial del plan</t>
+          <t>Resolver desde «Para resolver como dirección»</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Abra la ficha de DEM-001 → sección 4 → nueva versión: cambie las horas de un producto y apruebe; luego revise el producto y la bitácora.</t>
+          <t>En Mi trabajo resuelva uno de los casos demo con las cuatro decisiones.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Las horas del plan quedan como «horas planificadas»; las horas vendidas NO cambian (condición de la 3.ª ronda). La bitácora registra «horas planificadas», no «horas».</t>
+          <t>La sección concentra los ajustes de todos los cargos; cada decisión queda en el historial.</t>
         </is>
       </c>
       <c r="F13" s="19" t="n"/>
@@ -4002,17 +4130,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Verificar el bloqueo por coordinación</t>
+          <t>Verificar la integridad comercial del plan</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Intente aprobar el plan de DEM-003 (su coordinación está En ajuste).</t>
+          <t>Abra la ficha de DEM-001 → sección 4 → nueva versión: cambie las horas de un producto y apruebe; luego revise el producto y la bitácora.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>La aprobación se bloquea explicando que la coordinación debe resolverse primero (condición de la 3.ª ronda).</t>
+          <t>Las horas del plan quedan como «horas planificadas»; las horas vendidas NO cambian (condición de la 3.ª ronda). La bitácora registra «horas planificadas», no «horas».</t>
         </is>
       </c>
       <c r="F14" s="19" t="n"/>
@@ -4026,22 +4154,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
+          <t>Épica 4 · Plan de trabajo final</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Verificar la restricción de los demás cargos</t>
+          <t>Verificar el bloqueo por coordinación</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Cambie la sesión a Gestor de Datos 1: confirme que no ve Configuración ni valores en dinero y que Parametrización muestra «Módulo restringido» con la explicación.</t>
+          <t>Intente aprobar el plan de DEM-003 (su coordinación está En ajuste).</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>La restricción es integral: barra lateral, columnas de valor, tarifas de tarjetas y campo Valor facturado.</t>
+          <t>La aprobación se bloquea explicando que la coordinación debe resolverse primero (condición de la 3.ª ronda).</t>
         </is>
       </c>
       <c r="F15" s="19" t="n"/>
@@ -4055,22 +4183,22 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Aceptación de la versión final</t>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Firmar la aceptación de la versión final</t>
+          <t>Verificar la restricción de los demás cargos</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Termine las verificaciones de esta pestaña y diligencie su fila en la tabla «Decisión de salida a producción» de la pestaña «Resumen de observaciones» (Sí · Con ajustes menores · No), con nombre y fecha.</t>
+          <t>Cambie la sesión a Gestor de Datos 1: confirme que no ve Configuración ni valores en dinero y que Parametrización muestra «Módulo restringido» con la explicación.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>La v16 aplica los cambios acordados de la tercera ronda. Si algo quedó mal aplicado, regístrelo aquí; si todo está conforme, esta es la versión que sale a producción (piloto controlado con respaldo JSON semanal).</t>
+          <t>La restricción es integral: barra lateral, columnas de valor, tarifas de tarjetas y campo Valor facturado.</t>
         </is>
       </c>
       <c r="F16" s="19" t="n"/>
@@ -4078,32 +4206,61 @@
       <c r="H16" s="20" t="n"/>
       <c r="I16" s="20" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Firmar la aceptación de la versión final</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Termine las verificaciones de esta pestaña y diligencie su fila en la tabla «Decisión de salida a producción» de la pestaña «Resumen de observaciones» (Sí · Con ajustes menores · No), con nombre y fecha.</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>La v16 aplica los cambios acordados de la tercera ronda. Si algo quedó mal aplicado, regístrelo aquí; si todo está conforme, esta es la versión que sale a producción (piloto controlado con respaldo JSON semanal).</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Fuente: Especificación funcional y flujograma del proceso de gestión de proyectos, versión 1.1, Rehavid S.A.S. Ronda de aceptación sobre la versión 16 (final): modelo de administradores (CEO, Gerente, Director, Jefe), costos restringidos, y los hallazgos de la tercera ronda aplicados (plan con horas planificadas, coordinación bloqueante, ubicación obligatoria, reasignación entre gestores, calendario uniforme). Los pasos 1 a 11 corresponden al numeral 7 de la especificación. Traslade cada observación a la pestaña «Resumen de observaciones» con el N° de la fila.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I16"/>
+  <autoFilter ref="A9:I17"/>
   <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A18:I18"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F10:F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Seleccione: Sí, No, Parcial o No aplica." promptTitle="¿Funciona?" prompt="Seleccione: Sí, No, Parcial o No aplica." type="list">
+    <dataValidation sqref="F10:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Seleccione: Sí, No, Parcial o No aplica." promptTitle="¿Funciona?" prompt="Seleccione: Sí, No, Parcial o No aplica." type="list">
       <formula1>"Sí,No,Parcial,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="G10:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Califique con un entero de 1 a 5." promptTitle="Claridad (1-5)" prompt="1 = nada clara · 5 = totalmente clara." type="list">
+    <dataValidation sqref="G10:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Califique con un entero de 1 a 5." promptTitle="Claridad (1-5)" prompt="1 = nada clara · 5 = totalmente clara." type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
